--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/magallanes-y-antartica.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15522.32</v>
+        <v>15904.33</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2508.81</v>
+        <v>2497.81</v>
       </c>
     </row>
   </sheetData>
